--- a/www/download/IND.gdp.s.mv.zdW16.xlsx
+++ b/www/download/IND.gdp.s.mv.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7870.933</t>
+          <t>7870933371.67118</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7875.482</t>
+          <t>7875481947.48491</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7864.886</t>
+          <t>7864886010.7566</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8119.32</t>
+          <t>8119319995.66525</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8091.331</t>
+          <t>8091330604.31539</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8438.71</t>
+          <t>8438709661.17067</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>8730.93</t>
+          <t>8730929525.61658</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>9131.67</t>
+          <t>9131669599.54924</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9020.503</t>
+          <t>9020503042.20175</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>9283.393</t>
+          <t>9283393420.97856</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9359.16</t>
+          <t>9359159723.08198</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>9614.861</t>
+          <t>9614861155.47545</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>9414.544</t>
+          <t>9414543729.43245</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>9723.545</t>
+          <t>9723544995.86734</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>9753.689</t>
+          <t>9753688733.13505</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3184.8</t>
+          <t>3184800428.17491</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3170.239</t>
+          <t>3170239217.63259</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3112.534</t>
+          <t>3112534304.14413</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3134.971</t>
+          <t>3134970650.75014</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3154.712</t>
+          <t>3154711696.0629</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3116.829</t>
+          <t>3116829277.40687</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3114.064</t>
+          <t>3114063986.82157</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3172.135</t>
+          <t>3172134726.08532</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3232.791</t>
+          <t>3232791193.88891</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3120.432</t>
+          <t>3120431818.48127</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3125.263</t>
+          <t>3125263078.22587</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3174.199</t>
+          <t>3174199101.61736</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3157.72</t>
+          <t>3157720351.57556</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3143.277</t>
+          <t>3143276612.57288</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3146.869</t>
+          <t>3146869184.22086</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2698.292</t>
+          <t>2698291872.46098</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2710.764</t>
+          <t>2710763616.60758</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2660.55</t>
+          <t>2660549892.99879</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2638.34</t>
+          <t>2638340003.83444</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2643.238</t>
+          <t>2643237525.1341</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2622.959</t>
+          <t>2622958582.6215</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2658.026</t>
+          <t>2658026200.31574</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2693.045</t>
+          <t>2693045274.69151</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2722.109</t>
+          <t>2722108969.92773</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2659.827</t>
+          <t>2659827430.59279</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2670.522</t>
+          <t>2670521568.2849</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2740.527</t>
+          <t>2740526915.24889</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2737.224</t>
+          <t>2737224263.32177</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2720.216</t>
+          <t>2720215906.53791</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2720.836</t>
+          <t>2720835784.01712</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3749.698</t>
+          <t>3749697532.25763</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3703.578</t>
+          <t>3703577534.06697</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3702.531</t>
+          <t>3702530545.07319</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3685.673</t>
+          <t>3685673288.6053</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3713.934</t>
+          <t>3713934322.3377</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3706.656</t>
+          <t>3706655621.68365</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3845.061</t>
+          <t>3845061211.95176</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3934.222</t>
+          <t>3934221709.59554</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4136.295</t>
+          <t>4136294741.06204</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3804.531</t>
+          <t>3804530636.60816</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>3535.481</t>
+          <t>3535481208.07751</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>3430.774</t>
+          <t>3430774302.35543</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3308.836</t>
+          <t>3308836306.52582</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>3291.848</t>
+          <t>3291848445.48492</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3431.88</t>
+          <t>3431880034.30416</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>86975.447</t>
+          <t>86975447433.1493</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>85765.04</t>
+          <t>85765040198.9891</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>89268.229</t>
+          <t>89268228616.6197</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>90941.355</t>
+          <t>90941355411.9926</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>95505.6</t>
+          <t>95505599868.4065</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>97187.204</t>
+          <t>97187203899.8127</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>95422.724</t>
+          <t>95422724332.3174</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>97462.16</t>
+          <t>97462160330.3724</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>100215.655</t>
+          <t>100215655151.081</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>98748.929</t>
+          <t>98748929137.7656</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>101168.474</t>
+          <t>101168474123.069</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>100921.442</t>
+          <t>100921442336.904</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>101506.051</t>
+          <t>101506050613.234</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>103922.304</t>
+          <t>103922304150.585</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>105535.719</t>
+          <t>105535719297.727</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11664.947</t>
+          <t>11664946503.4405</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11678.471</t>
+          <t>11678470593.3175</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11877.712</t>
+          <t>11877711654.7646</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11944.459</t>
+          <t>11944459364.3361</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12151.603</t>
+          <t>12151603431.3342</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12271.599</t>
+          <t>12271599470.2647</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>12403.781</t>
+          <t>12403780586.7602</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>12587.988</t>
+          <t>12587987615.5463</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>12836.283</t>
+          <t>12836283035.7477</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12253.053</t>
+          <t>12253053485.4088</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>12567.016</t>
+          <t>12567016037.3404</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>12668.973</t>
+          <t>12668973393.3321</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13094.59</t>
+          <t>13094590383.918</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>13095.118</t>
+          <t>13095118495.1891</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>13690.608</t>
+          <t>13690608256.4918</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>994861.9</t>
+          <t>994861900174.557</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>997553.185</t>
+          <t>997553185289.72</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1013999.359</t>
+          <t>1013999359191.35</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>999085.301</t>
+          <t>999085301380.989</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1001218.754</t>
+          <t>1001218754043.79</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>999970.086</t>
+          <t>999970086166.46</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1036806.039</t>
+          <t>1036806039292.88</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1059170.482</t>
+          <t>1059170481631.55</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1097415.175</t>
+          <t>1097415174565.54</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1109161.092</t>
+          <t>1109161092311.59</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1106283.494</t>
+          <t>1106283493817.43</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1200325.632</t>
+          <t>1200325632096.01</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1207352.703</t>
+          <t>1207352703299.81</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1192792.842</t>
+          <t>1192792841732.42</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1169638.2</t>
+          <t>1169638200430.26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>222.547</t>
+          <t>222547086.021874</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>225.415</t>
+          <t>225414930.769334</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>225.472</t>
+          <t>225471585.33269</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>250.43</t>
+          <t>250430368.838078</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>249.793</t>
+          <t>249793130.458101</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>253.083</t>
+          <t>253082650.205455</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>253.318</t>
+          <t>253317815.882089</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>261.566</t>
+          <t>261565858.469471</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>264.958</t>
+          <t>264958413.31652</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>264.502</t>
+          <t>264502487.591403</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>252.915</t>
+          <t>252914913.403677</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>240.924</t>
+          <t>240923810.904615</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>224.839</t>
+          <t>224839162.55024</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>202.809</t>
+          <t>202809297.510654</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>193.479</t>
+          <t>193478537.56124</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5215.895</t>
+          <t>5215895068.51339</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4925.32</t>
+          <t>4925319895.33369</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4889.279</t>
+          <t>4889278779.13523</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4773.792</t>
+          <t>4773792200.30514</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4884.052</t>
+          <t>4884051512.68133</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4975.385</t>
+          <t>4975384561.5243</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4942.774</t>
+          <t>4942773963.50499</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>5008.895</t>
+          <t>5008894566.04545</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>5068.023</t>
+          <t>5068023132.13998</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4847.027</t>
+          <t>4847027325.43213</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>4846.98</t>
+          <t>4846979961.55058</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>4919.573</t>
+          <t>4919573132.37706</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4895.176</t>
+          <t>4895176110.62757</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>4865.366</t>
+          <t>4865366219.61712</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>4893.574</t>
+          <t>4893574075.36141</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27268.472</t>
+          <t>27268471961.4899</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26788.207</t>
+          <t>26788206573.5587</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26409.5</t>
+          <t>26409500179.7955</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25901.898</t>
+          <t>25901897981.7143</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25779.462</t>
+          <t>25779462436.6757</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25295.143</t>
+          <t>25295142971.4418</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>25673.257</t>
+          <t>25673257177.0877</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>26050.647</t>
+          <t>26050646572.2076</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>26329.344</t>
+          <t>26329344276.8118</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>25175.829</t>
+          <t>25175828625.5605</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>25818.226</t>
+          <t>25818225967.1286</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>26464.207</t>
+          <t>26464207073.5573</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>26596.598</t>
+          <t>26596597511.2707</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>26640.853</t>
+          <t>26640853430.3182</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>27114.519</t>
+          <t>27114518849.8424</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2162.536</t>
+          <t>2162536491.5631</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2182.247</t>
+          <t>2182246656.53073</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2155.54</t>
+          <t>2155539937.94832</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2104.673</t>
+          <t>2104673189.81556</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2075.759</t>
+          <t>2075759000.71623</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2084.874</t>
+          <t>2084873702.20321</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2125.552</t>
+          <t>2125552011.00408</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2118.778</t>
+          <t>2118777798.06614</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2121.941</t>
+          <t>2121940968.31571</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2037.041</t>
+          <t>2037040694.84096</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1959.677</t>
+          <t>1959677493.74723</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1973.018</t>
+          <t>1973017545.40415</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1937.597</t>
+          <t>1937597410.46853</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1944.043</t>
+          <t>1944042729.13806</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1963.066</t>
+          <t>1963066280.23548</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14435.041</t>
+          <t>14435041277.9848</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14834.436</t>
+          <t>14834435524.5254</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15137.925</t>
+          <t>15137925227.498</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15544.757</t>
+          <t>15544756900.028</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>15789.704</t>
+          <t>15789704215.7987</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>16177.637</t>
+          <t>16177637457.6443</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16475.891</t>
+          <t>16475890664.5509</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>16648.637</t>
+          <t>16648636573.5607</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>16125.718</t>
+          <t>16125717727.3991</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>14545.328</t>
+          <t>14545328021.0932</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>14061.92</t>
+          <t>14061919698.3481</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>13427.015</t>
+          <t>13427015031.3635</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>12472.738</t>
+          <t>12472738077.3081</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>11936.023</t>
+          <t>11936022730.1082</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>12031.483</t>
+          <t>12031483463.3219</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>653.313</t>
+          <t>653313121.730361</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>662.368</t>
+          <t>662367517.305403</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>667.492</t>
+          <t>667491654.153334</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>707.236</t>
+          <t>707236236.908044</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>708.971</t>
+          <t>708970903.444176</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>713.139</t>
+          <t>713139285.849883</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>741.497</t>
+          <t>741496941.710482</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>750.739</t>
+          <t>750738653.510219</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>716.757</t>
+          <t>716757120.149308</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>592.445</t>
+          <t>592445043.101207</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>559.244</t>
+          <t>559243805.208966</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>635.522</t>
+          <t>635522129.940804</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>612.478</t>
+          <t>612477513.767772</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>595.719</t>
+          <t>595719053.655805</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>607.174</t>
+          <t>607174401.134361</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2187.228</t>
+          <t>2187227686.27012</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2186.321</t>
+          <t>2186320765.38144</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2177.107</t>
+          <t>2177106596.22547</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2152.761</t>
+          <t>2152760906.44989</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2154.553</t>
+          <t>2154553456.03826</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2169.491</t>
+          <t>2169490759.72431</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2206.719</t>
+          <t>2206718695.85078</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2241.116</t>
+          <t>2241115750.34752</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2275.975</t>
+          <t>2275974609.99444</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2165.114</t>
+          <t>2165114214.68387</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2159.344</t>
+          <t>2159343802.53922</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2190.037</t>
+          <t>2190037357.52169</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2185.038</t>
+          <t>2185038018.63716</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2142.837</t>
+          <t>2142837338.63236</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2119.164</t>
+          <t>2119164279.37738</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16971.508</t>
+          <t>16971508241.1957</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16961.326</t>
+          <t>16961325891.697</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16550.12</t>
+          <t>16550120075.9172</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16487.799</t>
+          <t>16487799472.8652</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>16807.7</t>
+          <t>16807699721.342</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16837.287</t>
+          <t>16837287190.2714</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>16764.231</t>
+          <t>16764231327.4608</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>17147.916</t>
+          <t>17147916327.4675</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>17355.462</t>
+          <t>17355462181.8256</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>16975.156</t>
+          <t>16975156000.752</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>16917.761</t>
+          <t>16917761498.2304</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>17015.951</t>
+          <t>17015950771.2338</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>16935.501</t>
+          <t>16935500675.4427</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>16743.292</t>
+          <t>16743292474.491</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>16729.787</t>
+          <t>16729787239.6784</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>20180.486</t>
+          <t>20180485660.8344</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20010.231</t>
+          <t>20010230860.7269</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19924.273</t>
+          <t>19924273143.2232</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19706.173</t>
+          <t>19706172530.3448</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>19620.784</t>
+          <t>19620783548.2971</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>20071.996</t>
+          <t>20071995721.2687</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>20179.764</t>
+          <t>20179763889.5056</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>20189.42</t>
+          <t>20189419713.338</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>19996.673</t>
+          <t>19996672701.7467</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>20201.295</t>
+          <t>20201294932.5158</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>20228.88</t>
+          <t>20228879741.8376</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>20239.165</t>
+          <t>20239164659.8303</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>20682.515</t>
+          <t>20682515213.3546</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>20883.69</t>
+          <t>20883690266.7193</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>21410.079</t>
+          <t>21410079325.958</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4333.492</t>
+          <t>4333491918.53292</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4262.373</t>
+          <t>4262372547.55095</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4227.828</t>
+          <t>4227828196.36898</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4231.829</t>
+          <t>4231829174.66202</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4157.579</t>
+          <t>4157579059.82458</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4511.771</t>
+          <t>4511770903.20096</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4480.182</t>
+          <t>4480181608.76682</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4540.935</t>
+          <t>4540934594.14305</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4523.12</t>
+          <t>4523120085.16713</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4501.571</t>
+          <t>4501570658.78583</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>4001.695</t>
+          <t>4001695430.3924</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>3602.667</t>
+          <t>3602666828.41571</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>3273.293</t>
+          <t>3273293421.65186</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>3154.968</t>
+          <t>3154968418.52305</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3121.415</t>
+          <t>3121414831.96669</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5277.829</t>
+          <t>5277828590.35402</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5109.093</t>
+          <t>5109093077.5356</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5123.546</t>
+          <t>5123545693.09081</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4960.089</t>
+          <t>4960089074.31474</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4892.208</t>
+          <t>4892207655.27961</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4758.691</t>
+          <t>4758691249.93203</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4768.539</t>
+          <t>4768538784.31244</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4618.726</t>
+          <t>4618726432.74995</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4399.729</t>
+          <t>4399729393.58401</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4297.559</t>
+          <t>4297559419.15114</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3809.427</t>
+          <t>3809426685.30391</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3846.781</t>
+          <t>3846781155.252</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3668.841</t>
+          <t>3668840983.57889</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3560.468</t>
+          <t>3560468186.51475</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3726.306</t>
+          <t>3726305948.40497</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>102743.677</t>
+          <t>102743676849.126</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>108059.503</t>
+          <t>108059502815.42</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>113953.796</t>
+          <t>113953796434.844</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>120491.019</t>
+          <t>120491019446.615</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>121860.683</t>
+          <t>121860682680.697</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>110646.575</t>
+          <t>110646575372.814</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>103059.404</t>
+          <t>103059403758.666</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>105492.636</t>
+          <t>105492635634.461</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>106194.74</t>
+          <t>106194740165.901</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>107549.058</t>
+          <t>107549057962.187</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>111631.333</t>
+          <t>111631332687.487</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>111397.13</t>
+          <t>111397129577.328</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>122658.224</t>
+          <t>122658224485.25</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>136706.249</t>
+          <t>136706249484.089</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>152326.11</t>
+          <t>152326109562.284</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>759428.98</t>
+          <t>759428979889.746</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>779128.021</t>
+          <t>779128020914.484</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>800332.1</t>
+          <t>800332100250.639</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>822943.359</t>
+          <t>822943358524.539</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>846859.14</t>
+          <t>846859139878.412</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>850129.244</t>
+          <t>850129243775.652</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>846041.957</t>
+          <t>846041956515.516</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>843646.657</t>
+          <t>843646657380.445</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>843279.449</t>
+          <t>843279449043.228</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>844792.126</t>
+          <t>844792125997.793</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>849050.544</t>
+          <t>849050543738.707</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>856546.315</t>
+          <t>856546315280.055</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>971914.663</t>
+          <t>971914662850.404</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1083944.399</t>
+          <t>1083944398822.84</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1155520.751</t>
+          <t>1155520750857.5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1719.152</t>
+          <t>1719152112.37264</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1768.845</t>
+          <t>1768844925.70998</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1756.923</t>
+          <t>1756922889.43378</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1766.353</t>
+          <t>1766353277.19902</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1824.259</t>
+          <t>1824259064.78933</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1900.872</t>
+          <t>1900872209.89968</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1985.291</t>
+          <t>1985291498.91123</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2028.925</t>
+          <t>2028925395.47284</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1958.311</t>
+          <t>1958310708.40268</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1713.124</t>
+          <t>1713123989.26867</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1596.999</t>
+          <t>1596999472.23671</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1561.206</t>
+          <t>1561206165.79226</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1530.696</t>
+          <t>1530695606.85917</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1605.338</t>
+          <t>1605338221.70772</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1645.546</t>
+          <t>1645545806.55181</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>18959.061</t>
+          <t>18959061376.1308</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19140.995</t>
+          <t>19140994539.6157</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>19080.583</t>
+          <t>19080582855.3485</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19060.08</t>
+          <t>19060080257.6334</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>19270.575</t>
+          <t>19270575175.6172</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19252.979</t>
+          <t>19252979005.1711</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>19568.163</t>
+          <t>19568162577.9429</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>19757.706</t>
+          <t>19757706413.5773</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>19695.13</t>
+          <t>19695130102.4615</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>18563.053</t>
+          <t>18563053284.1125</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>18227.746</t>
+          <t>18227745962.5505</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>18193.23</t>
+          <t>18193230448.5615</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>17370.359</t>
+          <t>17370358665.3057</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>16789.864</t>
+          <t>16789864091.5348</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>16786.021</t>
+          <t>16786021262.2449</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>62255.156</t>
+          <t>62255156367.364</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60604.4</t>
+          <t>60604400453.8606</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>58692.411</t>
+          <t>58692411432.7743</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>58645.255</t>
+          <t>58645254546.1036</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>58611.895</t>
+          <t>58611894521.6298</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>58346.077</t>
+          <t>58346076600.9756</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>59008.904</t>
+          <t>59008903619.6537</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>58903.267</t>
+          <t>58903266550.6008</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>57766.553</t>
+          <t>57766552735.9515</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>54208.181</t>
+          <t>54208181050.2002</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>55119.421</t>
+          <t>55119420650.4738</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>55325.925</t>
+          <t>55325924568.4869</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>55703.891</t>
+          <t>55703891334.6835</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>54764.722</t>
+          <t>54764721875.9967</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>53755.444</t>
+          <t>53755443692.3521</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21624.575</t>
+          <t>21624575181.2611</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21369.976</t>
+          <t>21369976171.8863</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21710.541</t>
+          <t>21710540523.3118</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22028.568</t>
+          <t>22028567728.521</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22752.696</t>
+          <t>22752695840.3661</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>21816.202</t>
+          <t>21816202431.314</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>21820.82</t>
+          <t>21820820344.6363</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>21244.659</t>
+          <t>21244659387.5937</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>21245.835</t>
+          <t>21245834661.4116</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>22532.36</t>
+          <t>22532360036.0333</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>22613.357</t>
+          <t>22613357268.3337</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>22555.077</t>
+          <t>22555077413.0551</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>22369.251</t>
+          <t>22369250862.8657</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>23754.771</t>
+          <t>23754771480.187</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>24078.845</t>
+          <t>24078844845.7787</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1735.005</t>
+          <t>1735005427.53296</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1663.789</t>
+          <t>1663788974.94404</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1670.045</t>
+          <t>1670044944.64661</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1755.552</t>
+          <t>1755551742.44378</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1664.639</t>
+          <t>1664638798.08949</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1722.676</t>
+          <t>1722676106.20362</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1729.932</t>
+          <t>1729932271.93526</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1697.076</t>
+          <t>1697075696.90971</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1626.48</t>
+          <t>1626480261.94854</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1396.755</t>
+          <t>1396755355.38056</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1319.312</t>
+          <t>1319311579.83028</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1320.086</t>
+          <t>1320086024.64373</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1342.734</t>
+          <t>1342733974.73732</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1330.805</t>
+          <t>1330805264.88213</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1345.796</t>
+          <t>1345795593.90387</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>183.227</t>
+          <t>183227379.378413</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>188.68</t>
+          <t>188680470.160696</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>192.28</t>
+          <t>192280332.992993</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>197.283</t>
+          <t>197282736.492324</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>202.218</t>
+          <t>202218398.335872</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>201.241</t>
+          <t>201240813.289666</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>206.818</t>
+          <t>206817547.119214</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>216.554</t>
+          <t>216554368.897416</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>223.69</t>
+          <t>223689920.302062</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>215.381</t>
+          <t>215381448.142096</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>220.213</t>
+          <t>220213185.04891</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>226.008</t>
+          <t>226008092.050431</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>228.33</t>
+          <t>228329695.739664</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>229.703</t>
+          <t>229702925.482604</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>233.151</t>
+          <t>233150612.163868</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1087.065</t>
+          <t>1087064917.46053</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1133.508</t>
+          <t>1133508142.51104</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1110.253</t>
+          <t>1110252531.21965</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1104.928</t>
+          <t>1104927915.29629</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1037.766</t>
+          <t>1037766385.10905</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1029.682</t>
+          <t>1029681866.73143</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1118.239</t>
+          <t>1118239406.31331</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1074.641</t>
+          <t>1074641426.34498</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1112.889</t>
+          <t>1112889284.38409</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>886.09</t>
+          <t>886090210.364711</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>815.239</t>
+          <t>815238827.058381</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>851.159</t>
+          <t>851158919.574799</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>868.637</t>
+          <t>868637297.450085</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>876.294</t>
+          <t>876293996.157103</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>867.908</t>
+          <t>867908198.153711</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>43821.685</t>
+          <t>43821685015.263</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>42455.932</t>
+          <t>42455931779.2968</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>41929.4</t>
+          <t>41929399882.0835</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>43080.865</t>
+          <t>43080864970.2255</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>45475.995</t>
+          <t>45475995286.7534</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>45216.175</t>
+          <t>45216174601.7824</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>47481.677</t>
+          <t>47481677433.9022</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>48465.322</t>
+          <t>48465322060.1672</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>49200.412</t>
+          <t>49200411642.2272</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>46740.072</t>
+          <t>46740072407.9748</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>47580.813</t>
+          <t>47580812577.6006</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>47853.595</t>
+          <t>47853595217.6054</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>49203.97</t>
+          <t>49203969517.3913</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>48542.685</t>
+          <t>48542685264.3783</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>49050.056</t>
+          <t>49050056095.9473</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>155.239</t>
+          <t>155238501.593279</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>144.359</t>
+          <t>144359237.157618</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>148.126</t>
+          <t>148126067.111763</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>146.241</t>
+          <t>146241106.137746</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>135.525</t>
+          <t>135524941.602045</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>142.888</t>
+          <t>142887733.509116</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>135.961</t>
+          <t>135961278.577105</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>140.524</t>
+          <t>140524465.445019</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>149.993</t>
+          <t>149992852.241784</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>154.191</t>
+          <t>154190889.883983</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>154.584</t>
+          <t>154583745.740108</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>143.262</t>
+          <t>143261899.251418</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>139.232</t>
+          <t>139231526.94844</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>140.648</t>
+          <t>140647852.719091</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>137.544</t>
+          <t>137543752.704324</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4954.484</t>
+          <t>4954484148.23894</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5019.95</t>
+          <t>5019950222.35104</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>5063.955</t>
+          <t>5063954729.11876</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5039.554</t>
+          <t>5039553765.94892</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>4993.094</t>
+          <t>4993093788.96644</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>4956.828</t>
+          <t>4956828303.82586</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>4973.707</t>
+          <t>4973707301.612</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>5063.953</t>
+          <t>5063953146.51523</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>5163.371</t>
+          <t>5163370847.6249</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>5134.333</t>
+          <t>5134333145.41473</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>5075.677</t>
+          <t>5075677360.27047</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>5123.12</t>
+          <t>5123119628.46767</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>5069.102</t>
+          <t>5069102011.88042</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>5014.898</t>
+          <t>5014897705.7539</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>4956.517</t>
+          <t>4956517221.59343</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>19833.376</t>
+          <t>19833376173.2489</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20138.591</t>
+          <t>20138591114.0013</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18690.162</t>
+          <t>18690162384.6458</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18536.362</t>
+          <t>18536361633.7923</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>18672.631</t>
+          <t>18672631211.6492</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18969.998</t>
+          <t>18969997714.5414</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>19387.576</t>
+          <t>19387576444.1649</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>19814.672</t>
+          <t>19814672447.9898</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>20590.903</t>
+          <t>20590902940.2526</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>19994.973</t>
+          <t>19994972943.0377</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>19268.864</t>
+          <t>19268864002.7087</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>19266.3</t>
+          <t>19266299702.144</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>19065.862</t>
+          <t>19065862476.2563</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>19147.058</t>
+          <t>19147058369.7251</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>19113.58</t>
+          <t>19113579743.8022</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5772.581</t>
+          <t>5772581307.59647</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5767.367</t>
+          <t>5767367065.97202</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5699.286</t>
+          <t>5699286115.03581</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>5554.444</t>
+          <t>5554443575.41843</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5407.88</t>
+          <t>5407880288.88379</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>5280.587</t>
+          <t>5280586572.92968</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5214.264</t>
+          <t>5214264139.96345</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>5164.774</t>
+          <t>5164773838.96558</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>5057.571</t>
+          <t>5057571113.14379</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4864.009</t>
+          <t>4864008750.48118</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>4764.909</t>
+          <t>4764908823.31054</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>4626.571</t>
+          <t>4626570554.13595</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>4381.669</t>
+          <t>4381668768.32186</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>4292.685</t>
+          <t>4292684679.31078</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>4359.952</t>
+          <t>4359952190.72091</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>16448.757</t>
+          <t>16448756792.1136</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16348.987</t>
+          <t>16348987104.7056</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>13859.222</t>
+          <t>13859221921.048</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>14287.132</t>
+          <t>14287132324.8236</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>13589.929</t>
+          <t>13589929194.0882</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>13485.095</t>
+          <t>13485095414.5193</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>13148.076</t>
+          <t>13148076460.0079</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>13207.201</t>
+          <t>13207201357.8372</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>13036.412</t>
+          <t>13036411943.7992</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>12525.338</t>
+          <t>12525337596.4115</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>12588.832</t>
+          <t>12588831833.2764</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>12579.835</t>
+          <t>12579835062.9024</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>9471.056</t>
+          <t>9471056139.4012</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>9361.915</t>
+          <t>9361914861.6483</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>9368.349</t>
+          <t>9368349072.26997</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>96210.022</t>
+          <t>96210021644.4255</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>94412.758</t>
+          <t>94412757582.7893</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>93967.032</t>
+          <t>93967032030.0215</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>93884.825</t>
+          <t>93884825304.9212</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>93757.258</t>
+          <t>93757257503.0607</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>94143.695</t>
+          <t>94143694644.0518</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>94600.798</t>
+          <t>94600798364.7208</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>94694.782</t>
+          <t>94694781839.8861</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>86169.254</t>
+          <t>86169253633.5643</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>81033.181</t>
+          <t>81033181485.5148</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>81042.682</t>
+          <t>81042681771.862</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>78909.443</t>
+          <t>78909443048.0438</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>80534.488</t>
+          <t>80534487805.5157</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>76672.04</t>
+          <t>76672039553.3559</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>73922.048</t>
+          <t>73922047579.9231</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2095.012</t>
+          <t>2095011792.09451</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2088.105</t>
+          <t>2088104703.93873</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1984.313</t>
+          <t>1984313074.92189</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1928.422</t>
+          <t>1928422270.56475</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1956.209</t>
+          <t>1956209121.92304</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1959.133</t>
+          <t>1959132959.12392</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1960.891</t>
+          <t>1960891402.37788</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1979.939</t>
+          <t>1979939248.17767</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2063.038</t>
+          <t>2063038455.15895</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1919.778</t>
+          <t>1919778365.25565</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1933.059</t>
+          <t>1933059370.86262</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1941.483</t>
+          <t>1941483091.84005</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1904.229</t>
+          <t>1904228926.16946</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1875.908</t>
+          <t>1875908402.53186</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1891.869</t>
+          <t>1891868825.27547</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>926.891</t>
+          <t>926890642.993233</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>910.402</t>
+          <t>910401924.908224</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>926.483</t>
+          <t>926482502.741757</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>915.306</t>
+          <t>915305770.486015</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>926.122</t>
+          <t>926121796.757386</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>903.784</t>
+          <t>903783791.794445</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>892.806</t>
+          <t>892806178.514439</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>907.2</t>
+          <t>907199853.997014</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>936.862</t>
+          <t>936862278.920497</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>901.729</t>
+          <t>901728605.568638</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>885.547</t>
+          <t>885547200.056221</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>855.644</t>
+          <t>855643604.65616</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>827.913</t>
+          <t>827913488.079578</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>827.892</t>
+          <t>827892490.524408</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>848.993</t>
+          <t>848993373.903613</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3970.044</t>
+          <t>3970044435.39375</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3988.675</t>
+          <t>3988674593.11153</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3947.939</t>
+          <t>3947939151.08072</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>3887.624</t>
+          <t>3887623558.08765</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3910.862</t>
+          <t>3910861775.91776</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3890.608</t>
+          <t>3890607843.57128</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>3910.336</t>
+          <t>3910335794.60349</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4008.546</t>
+          <t>4008545851.40325</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4069.854</t>
+          <t>4069853848.94016</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3924.675</t>
+          <t>3924675230.5949</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>3982.362</t>
+          <t>3982362090.48572</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4076.556</t>
+          <t>4076555753.69236</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4058.206</t>
+          <t>4058206283.19629</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4057.213</t>
+          <t>4057213471.53876</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>4104.404</t>
+          <t>4104403761.36511</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>30908.847</t>
+          <t>30908847141.3551</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30913.859</t>
+          <t>30913858730.9283</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>28746.786</t>
+          <t>28746785708.734</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>27759.585</t>
+          <t>27759585499.9764</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>28199.084</t>
+          <t>28199084405.1726</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>27806.896</t>
+          <t>27806896128.0379</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>26631.491</t>
+          <t>26631491042.7846</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>25045.639</t>
+          <t>25045639184.3616</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>25512.305</t>
+          <t>25512305405.8168</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>24991.77</t>
+          <t>24991769801.2339</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>26907.511</t>
+          <t>26907510632.407</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>28782.969</t>
+          <t>28782969323.4627</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>31137.553</t>
+          <t>31137552862.3905</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>33459.636</t>
+          <t>33459636392.7632</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>37478.572</t>
+          <t>37478572296.7034</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18642.244</t>
+          <t>18642244278.7469</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17267.094</t>
+          <t>17267094273.9098</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>18295.214</t>
+          <t>18295214458.1776</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18604.784</t>
+          <t>18604784057.1434</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>19037.612</t>
+          <t>19037611620.3775</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>18855.06</t>
+          <t>18855059890.7979</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>19441.2</t>
+          <t>19441200414.4775</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>19625.532</t>
+          <t>19625531558.9802</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>19149.03</t>
+          <t>19149030428.7835</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>19096.669</t>
+          <t>19096669028.5602</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>20241.646</t>
+          <t>20241646359.4972</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>19615.647</t>
+          <t>19615647409.1686</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>19896.468</t>
+          <t>19896468201.7249</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>20132.438</t>
+          <t>20132437651.2511</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>20559.078</t>
+          <t>20559078341.4519</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>93651.46</t>
+          <t>93651460046.8406</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>92449.104</t>
+          <t>92449103650.838</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>90422.747</t>
+          <t>90422746621.2516</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>89482.021</t>
+          <t>89482021258.212</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>90584.373</t>
+          <t>90584372586.2988</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>92030.874</t>
+          <t>92030874273.2381</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>94487.459</t>
+          <t>94487458845.8295</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>95734.569</t>
+          <t>95734568757.6579</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>94485.557</t>
+          <t>94485557183.5265</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>87988.053</t>
+          <t>87988053440.3063</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>87876.502</t>
+          <t>87876501686.0968</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>89168.115</t>
+          <t>89168114680.1731</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>91095.149</t>
+          <t>91095148913.1289</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>92757.729</t>
+          <t>92757728762.9651</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>95243.743</t>
+          <t>95243742928.2836</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1495405.662</t>
+          <t>1495405661626.89</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1537946.392</t>
+          <t>1537946392370.84</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1618620.709</t>
+          <t>1618620708679.12</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1666489.581</t>
+          <t>1666489580602.14</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1711911.731</t>
+          <t>1711911730700.66</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1738771.425</t>
+          <t>1738771424864.42</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1791656.776</t>
+          <t>1791656775591.68</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1822542.663</t>
+          <t>1822542663230.35</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1865839.514</t>
+          <t>1865839513829.65</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1889678.377</t>
+          <t>1889678377153.93</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1906043.652</t>
+          <t>1906043651903.69</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1988971.928</t>
+          <t>1988971928040.04</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2103441.37</t>
+          <t>2103441370451.62</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2208589.901</t>
+          <t>2208589900899.68</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2298779.392</t>
+          <t>2298779391713.35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4019736.05</t>
+          <t>4019736050217.03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4080643.5</t>
+          <t>4080643500214.89</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4197843.241</t>
+          <t>4197843240850.81</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4260989.155</t>
+          <t>4260989155275.51</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>4343438.05</t>
+          <t>4343438050187.65</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>4363869.731</t>
+          <t>4363869730746.82</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>4447440.727</t>
+          <t>4447440727332.58</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>4505719.773</t>
+          <t>4505719773026.27</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>4580993.161</t>
+          <t>4580993161294.67</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>4593029.174</t>
+          <t>4593029174128.79</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>4619816.005</t>
+          <t>4619816005464.27</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>4804952.373</t>
+          <t>4804952373344.11</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>5055876.009</t>
+          <t>5055876008989.74</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>5273824.206</t>
+          <t>5273824206470.04</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>5435889.025</t>
+          <t>5435889025427.87</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1870.236</t>
+          <t>1870236338.19224</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1803.921</t>
+          <t>1803920705.62594</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1806.089</t>
+          <t>1806089207.18025</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1786.246</t>
+          <t>1786245517.06687</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1867.918</t>
+          <t>1867918165.0958</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1857.111</t>
+          <t>1857110779.42097</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1871.932</t>
+          <t>1871931880.34484</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1884.944</t>
+          <t>1884943929.55098</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1954.647</t>
+          <t>1954646692.04246</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1902.391</t>
+          <t>1902391364.12336</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1824.623</t>
+          <t>1824622873.9101</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1768.753</t>
+          <t>1768753357.6259</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1667.031</t>
+          <t>1667030754.46954</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1613.196</t>
+          <t>1613196319.4364</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1633.011</t>
+          <t>1633010946.27834</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3607.538</t>
+          <t>3607537750.59297</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3541.509</t>
+          <t>3541508544.43799</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3478.796</t>
+          <t>3478796192.19108</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>3478.431</t>
+          <t>3478431291.51233</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3533.849</t>
+          <t>3533848945.12316</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3569.216</t>
+          <t>3569215551.08921</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3634.397</t>
+          <t>3634396990.94106</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>3680.407</t>
+          <t>3680407279.16667</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>3726.831</t>
+          <t>3726830902.30611</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>3690.704</t>
+          <t>3690704255.56561</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>3730.638</t>
+          <t>3730637801.94872</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>3827.466</t>
+          <t>3827466463.96165</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>3866.233</t>
+          <t>3866233328.92341</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>3873.601</t>
+          <t>3873600574.90945</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>3925.544</t>
+          <t>3925543690.4045</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1811.709</t>
+          <t>1811708660.88038</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1784.687</t>
+          <t>1784686562.74579</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1784.169</t>
+          <t>1784168646.7396</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1764.478</t>
+          <t>1764478461.78814</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1794.372</t>
+          <t>1794371980.33151</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1822.272</t>
+          <t>1822272365.42764</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1879.502</t>
+          <t>1879502211.08376</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>1967.909</t>
+          <t>1967908994.21834</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2028.019</t>
+          <t>2028019102.78388</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1998.675</t>
+          <t>1998674666.50442</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1994.464</t>
+          <t>1994463505.61309</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2034.281</t>
+          <t>2034281220.6357</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2073.41</t>
+          <t>2073409714.54964</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2103.397</t>
+          <t>2103396570.77324</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2128.955</t>
+          <t>2128954509.95639</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gdp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
